--- a/refs/heads/main/StructureDefinition-IdentidadGenero.xlsx
+++ b/refs/heads/main/StructureDefinition-IdentidadGenero.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:32:50+00:00</t>
+    <t>2023-01-19T00:52:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
